--- a/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:25:56+00:00</t>
+    <t>2026-04-08T14:49:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,18 +130,6 @@
   </si>
   <si>
     <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root-uuid</t>
-  </si>
-  <si>
-    <t>II.root (UUID sans extension)</t>
-  </si>
-  <si>
-    <t>II.root-oid</t>
-  </si>
-  <si>
-    <t>II.root (OID sans extension)</t>
   </si>
   <si>
     <t>II.assigningAuthorityName</t>
@@ -412,7 +400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -485,19 +473,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -505,16 +493,16 @@
         <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>37</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -522,67 +510,16 @@
         <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>37</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:49:56+00:00</t>
+    <t>2026-04-08T15:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T15:17:01+00:00</t>
+    <t>2026-04-08T15:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T15:16:22+00:00</t>
+    <t>2026-04-08T15:36:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/fsh-datatypes/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T15:36:08+00:00</t>
+    <t>2026-04-09T07:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
